--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126483257</v>
+        <v>126480896</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464760</v>
+        <v>464743</v>
       </c>
       <c r="R6" t="n">
-        <v>6784613</v>
+        <v>6784623</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,22 +1203,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126480896</v>
+        <v>126485580</v>
       </c>
       <c r="B7" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,37 +1226,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464743</v>
+        <v>464777</v>
       </c>
       <c r="R7" t="n">
-        <v>6784623</v>
+        <v>6784791</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,12 +1310,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126484892</v>
+        <v>126483257</v>
       </c>
       <c r="B9" t="n">
         <v>78980</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464806</v>
+        <v>464760</v>
       </c>
       <c r="R9" t="n">
-        <v>6784704</v>
+        <v>6784613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126484941</v>
+        <v>126484892</v>
       </c>
       <c r="B10" t="n">
         <v>78980</v>
@@ -1567,14 +1567,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464775</v>
+        <v>464806</v>
       </c>
       <c r="R10" t="n">
-        <v>6784702</v>
+        <v>6784704</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,19 +1631,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126485580</v>
+        <v>126484941</v>
       </c>
       <c r="B11" t="n">
         <v>78980</v>
@@ -1674,17 +1674,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464777</v>
+        <v>464775</v>
       </c>
       <c r="R11" t="n">
-        <v>6784791</v>
+        <v>6784702</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,22 +1738,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126481544</v>
+        <v>126480624</v>
       </c>
       <c r="B12" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464778</v>
+        <v>464766</v>
       </c>
       <c r="R12" t="n">
-        <v>6784647</v>
+        <v>6784628</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126480624</v>
+        <v>126481544</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464766</v>
+        <v>464778</v>
       </c>
       <c r="R13" t="n">
-        <v>6784628</v>
+        <v>6784647</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2509,32 +2509,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126483693</v>
+        <v>126481969</v>
       </c>
       <c r="B19" t="n">
-        <v>98278</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464741</v>
+        <v>464778</v>
       </c>
       <c r="R19" t="n">
-        <v>6784664</v>
+        <v>6784647</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,32 +2616,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126481969</v>
+        <v>126483693</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>98278</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464778</v>
+        <v>464741</v>
       </c>
       <c r="R20" t="n">
-        <v>6784647</v>
+        <v>6784664</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126481494</v>
+        <v>126484773</v>
       </c>
       <c r="B21" t="n">
         <v>78980</v>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464766</v>
+        <v>464760</v>
       </c>
       <c r="R21" t="n">
-        <v>6784648</v>
+        <v>6784680</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126484773</v>
+        <v>126481494</v>
       </c>
       <c r="B22" t="n">
         <v>78980</v>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464760</v>
+        <v>464766</v>
       </c>
       <c r="R22" t="n">
-        <v>6784680</v>
+        <v>6784648</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -5198,45 +5198,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126482525</v>
+        <v>126485023</v>
       </c>
       <c r="B44" t="n">
-        <v>103803</v>
+        <v>78980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västersvedbäcken, Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464743</v>
+        <v>464772</v>
       </c>
       <c r="R44" t="n">
-        <v>6784670</v>
+        <v>6784708</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5305,45 +5305,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126485023</v>
+        <v>126482525</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>103803</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Västersvedbäcken, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464772</v>
+        <v>464743</v>
       </c>
       <c r="R45" t="n">
-        <v>6784708</v>
+        <v>6784670</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126480896</v>
+        <v>126485580</v>
       </c>
       <c r="B6" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,37 +1119,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464743</v>
+        <v>464777</v>
       </c>
       <c r="R6" t="n">
-        <v>6784623</v>
+        <v>6784791</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,19 +1203,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126485580</v>
+        <v>126483257</v>
       </c>
       <c r="B7" t="n">
         <v>78980</v>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464777</v>
+        <v>464760</v>
       </c>
       <c r="R7" t="n">
-        <v>6784791</v>
+        <v>6784613</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126485359</v>
+        <v>126484892</v>
       </c>
       <c r="B8" t="n">
         <v>78980</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464793</v>
+        <v>464806</v>
       </c>
       <c r="R8" t="n">
-        <v>6784773</v>
+        <v>6784704</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126483257</v>
+        <v>126480896</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,34 +1440,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464760</v>
+        <v>464743</v>
       </c>
       <c r="R9" t="n">
-        <v>6784613</v>
+        <v>6784623</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,19 +1524,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126484892</v>
+        <v>126484941</v>
       </c>
       <c r="B10" t="n">
         <v>78980</v>
@@ -1567,14 +1567,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464806</v>
+        <v>464775</v>
       </c>
       <c r="R10" t="n">
-        <v>6784704</v>
+        <v>6784702</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,19 +1631,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126484941</v>
+        <v>126485359</v>
       </c>
       <c r="B11" t="n">
         <v>78980</v>
@@ -1674,14 +1674,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464775</v>
+        <v>464793</v>
       </c>
       <c r="R11" t="n">
-        <v>6784702</v>
+        <v>6784773</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,22 +1738,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126480624</v>
+        <v>126481544</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464766</v>
+        <v>464778</v>
       </c>
       <c r="R12" t="n">
-        <v>6784628</v>
+        <v>6784647</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126481544</v>
+        <v>126480624</v>
       </c>
       <c r="B13" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464778</v>
+        <v>464766</v>
       </c>
       <c r="R13" t="n">
-        <v>6784647</v>
+        <v>6784628</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,7 +2076,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126485112</v>
+        <v>126485104</v>
       </c>
       <c r="B15" t="n">
         <v>78980</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126485040</v>
+        <v>126481969</v>
       </c>
       <c r="B18" t="n">
         <v>78980</v>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464849</v>
+        <v>464778</v>
       </c>
       <c r="R18" t="n">
-        <v>6784700</v>
+        <v>6784647</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126481969</v>
+        <v>126485040</v>
       </c>
       <c r="B19" t="n">
         <v>78980</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464778</v>
+        <v>464849</v>
       </c>
       <c r="R19" t="n">
-        <v>6784647</v>
+        <v>6784700</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3156,48 +3156,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126485124</v>
+        <v>126485741</v>
       </c>
       <c r="B25" t="n">
-        <v>80119</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464772</v>
+        <v>464743</v>
       </c>
       <c r="R25" t="n">
-        <v>6784708</v>
+        <v>6784824</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3236,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie på ca 50 meter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3251,57 +3256,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126480574</v>
+        <v>126485124</v>
       </c>
       <c r="B26" t="n">
-        <v>78738</v>
+        <v>80119</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464743</v>
+        <v>464772</v>
       </c>
       <c r="R26" t="n">
-        <v>6784623</v>
+        <v>6784708</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3343,7 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3477,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126485741</v>
+        <v>126480574</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3488,37 +3493,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
         <v>464743</v>
       </c>
       <c r="R28" t="n">
-        <v>6784824</v>
+        <v>6784623</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3547,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3557,12 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie på ca 50 meter.</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,12 +3577,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126483268</v>
+        <v>126485629</v>
       </c>
       <c r="B31" t="n">
         <v>78980</v>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464732</v>
+        <v>464769</v>
       </c>
       <c r="R31" t="n">
-        <v>6784658</v>
+        <v>6784801</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3910,41 +3910,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126483802</v>
+        <v>126483268</v>
       </c>
       <c r="B32" t="n">
-        <v>97241</v>
+        <v>78980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>224363</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464766</v>
+        <v>464732</v>
       </c>
       <c r="R32" t="n">
-        <v>6784682</v>
+        <v>6784658</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3976,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3986,7 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4001,12 +4005,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4119,10 +4123,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126485629</v>
+        <v>126483169</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4130,34 +4134,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464769</v>
+        <v>464732</v>
       </c>
       <c r="R34" t="n">
-        <v>6784801</v>
+        <v>6784654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4226,50 +4235,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126483169</v>
+        <v>126483802</v>
       </c>
       <c r="B35" t="n">
-        <v>57654</v>
+        <v>97241</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>224363</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464732</v>
+        <v>464766</v>
       </c>
       <c r="R35" t="n">
-        <v>6784654</v>
+        <v>6784682</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4326,12 +4326,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4444,32 +4444,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126483158</v>
+        <v>126480564</v>
       </c>
       <c r="B37" t="n">
-        <v>8447</v>
+        <v>79012</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4479,10 +4479,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464732</v>
+        <v>464766</v>
       </c>
       <c r="R37" t="n">
-        <v>6784654</v>
+        <v>6784628</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4551,32 +4551,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126480564</v>
+        <v>126483158</v>
       </c>
       <c r="B38" t="n">
-        <v>79012</v>
+        <v>8447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464766</v>
+        <v>464732</v>
       </c>
       <c r="R38" t="n">
-        <v>6784628</v>
+        <v>6784654</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4658,32 +4658,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126481132</v>
+        <v>126482418</v>
       </c>
       <c r="B39" t="n">
-        <v>78739</v>
+        <v>79004</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4696,7 +4696,7 @@
         <v>464743</v>
       </c>
       <c r="R39" t="n">
-        <v>6784623</v>
+        <v>6784670</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4765,32 +4765,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126482418</v>
+        <v>126481132</v>
       </c>
       <c r="B40" t="n">
-        <v>79004</v>
+        <v>78739</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4803,7 +4803,7 @@
         <v>464743</v>
       </c>
       <c r="R40" t="n">
-        <v>6784670</v>
+        <v>6784623</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4017,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126492740</v>
+        <v>126483169</v>
       </c>
       <c r="B33" t="n">
-        <v>79012</v>
+        <v>57654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4028,40 +4028,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464775</v>
+        <v>464732</v>
       </c>
       <c r="R33" t="n">
         <v>6784654</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4088,14 +4090,19 @@
           <t>2025-07-07</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4104,69 +4111,59 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126483169</v>
+        <v>126483802</v>
       </c>
       <c r="B34" t="n">
-        <v>57654</v>
+        <v>97241</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>224363</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464732</v>
+        <v>464766</v>
       </c>
       <c r="R34" t="n">
-        <v>6784654</v>
+        <v>6784682</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4198,7 +4195,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4208,7 +4205,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4223,56 +4220,63 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126483802</v>
+        <v>126492740</v>
       </c>
       <c r="B35" t="n">
-        <v>97241</v>
+        <v>79012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>224363</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464766</v>
+        <v>464775</v>
       </c>
       <c r="R35" t="n">
-        <v>6784682</v>
+        <v>6784654</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4299,19 +4303,14 @@
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:01</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4320,18 +4319,19 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5410,6 +5410,2380 @@
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126585639</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>464704</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6784647</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126585280</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>464749</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6784609</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126589776</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>464839</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6784720</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126586836</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>464689</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6784645</v>
+      </c>
+      <c r="S49" t="n">
+        <v>50</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Miljöbild, rullstensås</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126586891</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>464671</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6784711</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126590186</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>464816</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6784753</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126590922</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>464730</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6784826</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Med bild garnlav bandning</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126585619</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>464704</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6784647</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126586092</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>464712</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6784680</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126585460</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>464725</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6784623</v>
+      </c>
+      <c r="S55" t="n">
+        <v>50</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126589735</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>464857</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6784712</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126591332</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>464744</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6784847</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126591518</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>464757</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6784856</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126585736</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>464720</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6784658</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126589398</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>464858</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6784712</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126585897</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>464732</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6784658</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126586980</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>464671</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6784711</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126589767</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>464839</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6784720</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126586650</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>464649</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6784725</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126586084</v>
+      </c>
+      <c r="B65" t="n">
+        <v>75075</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>464712</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6784680</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126585359</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>464766</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6784628</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126586047</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>464730</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6784662</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -2290,50 +2290,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126484808</v>
+        <v>126481969</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464775</v>
+        <v>464778</v>
       </c>
       <c r="R17" t="n">
-        <v>6784702</v>
+        <v>6784647</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2360,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2370,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,19 +2385,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126481969</v>
+        <v>126485040</v>
       </c>
       <c r="B18" t="n">
         <v>78980</v>
@@ -2437,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464778</v>
+        <v>464849</v>
       </c>
       <c r="R18" t="n">
-        <v>6784647</v>
+        <v>6784700</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,45 +2504,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126485040</v>
+        <v>126484808</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464849</v>
+        <v>464775</v>
       </c>
       <c r="R19" t="n">
-        <v>6784700</v>
+        <v>6784702</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,12 +2604,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -6920,10 +6920,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126589398</v>
+        <v>126585897</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6931,34 +6931,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464858</v>
+        <v>464732</v>
       </c>
       <c r="R60" t="n">
-        <v>6784712</v>
+        <v>6784658</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6990,7 +6995,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7000,7 +7005,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7027,10 +7032,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126585897</v>
+        <v>126586980</v>
       </c>
       <c r="B61" t="n">
-        <v>57654</v>
+        <v>79598</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7038,39 +7043,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464732</v>
+        <v>464671</v>
       </c>
       <c r="R61" t="n">
-        <v>6784658</v>
+        <v>6784711</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126586980</v>
+        <v>126589398</v>
       </c>
       <c r="B62" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,21 +7150,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464671</v>
+        <v>464858</v>
       </c>
       <c r="R62" t="n">
-        <v>6784711</v>
+        <v>6784712</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -4017,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126483169</v>
+        <v>126492740</v>
       </c>
       <c r="B33" t="n">
-        <v>57654</v>
+        <v>79012</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4028,42 +4028,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464732</v>
+        <v>464775</v>
       </c>
       <c r="R33" t="n">
         <v>6784654</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4090,19 +4088,14 @@
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:56</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4111,59 +4104,69 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126483802</v>
+        <v>126483169</v>
       </c>
       <c r="B34" t="n">
-        <v>97241</v>
+        <v>57654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>224363</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464766</v>
+        <v>464732</v>
       </c>
       <c r="R34" t="n">
-        <v>6784682</v>
+        <v>6784654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4195,7 +4198,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4205,7 +4208,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,63 +4223,56 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126492740</v>
+        <v>126483802</v>
       </c>
       <c r="B35" t="n">
-        <v>79012</v>
+        <v>97241</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>224363</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464775</v>
+        <v>464766</v>
       </c>
       <c r="R35" t="n">
-        <v>6784654</v>
+        <v>6784682</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4303,14 +4299,19 @@
           <t>2025-07-07</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4319,19 +4320,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -5522,7 +5522,7 @@
         <v>126589776</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>126586891</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>126590186</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5840,10 +5840,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126590867</v>
+        <v>126585619</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5875,10 +5875,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464730</v>
+        <v>464704</v>
       </c>
       <c r="R50" t="n">
-        <v>6784826</v>
+        <v>6784647</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5947,10 +5947,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126585619</v>
+        <v>126590867</v>
       </c>
       <c r="B51" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464704</v>
+        <v>464730</v>
       </c>
       <c r="R51" t="n">
-        <v>6784647</v>
+        <v>6784826</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6057,7 +6057,7 @@
         <v>126585460</v>
       </c>
       <c r="B52" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>126591332</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>126589735</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>126591518</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>126585536</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>126585736</v>
       </c>
       <c r="B57" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>126589398</v>
       </c>
       <c r="B58" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>126585258</v>
       </c>
       <c r="B59" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>126586650</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>126586047</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>126586092</v>
       </c>
       <c r="B64" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>126586980</v>
       </c>
       <c r="B65" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>126586084</v>
       </c>
       <c r="B67" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>127020539</v>
       </c>
       <c r="B68" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>127020521</v>
       </c>
       <c r="B69" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -5522,7 +5522,7 @@
         <v>126589776</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>126586891</v>
       </c>
       <c r="B48" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>126590186</v>
       </c>
       <c r="B49" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>126585619</v>
       </c>
       <c r="B50" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>126590867</v>
       </c>
       <c r="B51" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>126585460</v>
       </c>
       <c r="B52" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>126591332</v>
       </c>
       <c r="B53" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>126589735</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>126591518</v>
       </c>
       <c r="B55" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>126585536</v>
       </c>
       <c r="B56" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>126585736</v>
       </c>
       <c r="B57" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>126589398</v>
       </c>
       <c r="B58" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>126585258</v>
       </c>
       <c r="B59" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>126586650</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>126586047</v>
       </c>
       <c r="B63" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>126586092</v>
       </c>
       <c r="B64" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>126586980</v>
       </c>
       <c r="B65" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>126586084</v>
       </c>
       <c r="B67" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>127020539</v>
       </c>
       <c r="B68" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>127020521</v>
       </c>
       <c r="B69" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -7450,10 +7450,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126586980</v>
+        <v>126585897</v>
       </c>
       <c r="B65" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7461,34 +7461,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464671</v>
+        <v>464732</v>
       </c>
       <c r="R65" t="n">
-        <v>6784711</v>
+        <v>6784658</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7557,10 +7562,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126585897</v>
+        <v>126586980</v>
       </c>
       <c r="B66" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7568,39 +7573,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464732</v>
+        <v>464671</v>
       </c>
       <c r="R66" t="n">
-        <v>6784658</v>
+        <v>6784711</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -7450,10 +7450,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126585897</v>
+        <v>126586980</v>
       </c>
       <c r="B65" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7461,39 +7461,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464732</v>
+        <v>464671</v>
       </c>
       <c r="R65" t="n">
-        <v>6784658</v>
+        <v>6784711</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7562,10 +7557,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126586980</v>
+        <v>126585897</v>
       </c>
       <c r="B66" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7573,34 +7568,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464671</v>
+        <v>464732</v>
       </c>
       <c r="R66" t="n">
-        <v>6784711</v>
+        <v>6784658</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -7788,7 +7788,7 @@
         <v>127020539</v>
       </c>
       <c r="B68" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>127020521</v>
       </c>
       <c r="B69" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7996,6 +7996,113 @@
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127531842</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>464850</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6784699</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -7788,7 +7788,7 @@
         <v>127020539</v>
       </c>
       <c r="B68" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>127020521</v>
       </c>
       <c r="B69" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -7788,7 +7788,7 @@
         <v>127020539</v>
       </c>
       <c r="B68" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>127020521</v>
       </c>
       <c r="B69" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>127531842</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -7788,7 +7788,7 @@
         <v>127020539</v>
       </c>
       <c r="B68" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>127020521</v>
       </c>
       <c r="B69" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -8001,7 +8001,7 @@
         <v>127531842</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -8001,7 +8001,7 @@
         <v>127531842</v>
       </c>
       <c r="B70" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -5522,7 +5522,7 @@
         <v>126589776</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>126586891</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>126590186</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>126585619</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>126590867</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>126585460</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>126591332</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>126589735</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>126591518</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>126585536</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>126585736</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>126589398</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>126585258</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>126586650</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>126586047</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>126586092</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>126586980</v>
       </c>
       <c r="B65" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>126586084</v>
       </c>
       <c r="B67" t="n">
-        <v>75138</v>
+        <v>75135</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>127020539</v>
       </c>
       <c r="B68" t="n">
-        <v>97339</v>
+        <v>97320</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>127020521</v>
       </c>
       <c r="B69" t="n">
-        <v>97333</v>
+        <v>97314</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -5522,7 +5522,7 @@
         <v>126589776</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>126586891</v>
       </c>
       <c r="B48" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>126590186</v>
       </c>
       <c r="B49" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>126585619</v>
       </c>
       <c r="B50" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>126590867</v>
       </c>
       <c r="B51" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>126585460</v>
       </c>
       <c r="B52" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>126591332</v>
       </c>
       <c r="B53" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>126589735</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>126591518</v>
       </c>
       <c r="B55" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>126585536</v>
       </c>
       <c r="B56" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>126585736</v>
       </c>
       <c r="B57" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>126589398</v>
       </c>
       <c r="B58" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>126585258</v>
       </c>
       <c r="B59" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>126586650</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>126586047</v>
       </c>
       <c r="B63" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>126586092</v>
       </c>
       <c r="B64" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>126586980</v>
       </c>
       <c r="B65" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>126586084</v>
       </c>
       <c r="B67" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>127020539</v>
       </c>
       <c r="B68" t="n">
-        <v>97320</v>
+        <v>97339</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>127020521</v>
       </c>
       <c r="B69" t="n">
-        <v>97314</v>
+        <v>97333</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126481487</v>
+        <v>126480564</v>
       </c>
       <c r="B2" t="n">
-        <v>79569</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
         <v>464766</v>
       </c>
       <c r="R2" t="n">
-        <v>6784648</v>
+        <v>6784628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126485146</v>
+        <v>126485267</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464765</v>
+        <v>464793</v>
       </c>
       <c r="R3" t="n">
-        <v>6784693</v>
+        <v>6784773</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126485702</v>
+        <v>126492740</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,37 +900,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464760</v>
+        <v>464775</v>
       </c>
       <c r="R4" t="n">
-        <v>6784816</v>
+        <v>6784654</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,19 +960,14 @@
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:56</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,28 +976,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126482486</v>
+        <v>126492750</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,37 +1006,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464743</v>
+        <v>464757</v>
       </c>
       <c r="R5" t="n">
-        <v>6784670</v>
+        <v>6784808</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,19 +1066,14 @@
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:31</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:31</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,28 +1082,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126484892</v>
+        <v>126492793</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,37 +1112,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464806</v>
+        <v>464714</v>
       </c>
       <c r="R6" t="n">
-        <v>6784704</v>
+        <v>6784832</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,19 +1172,14 @@
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:56</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,28 +1188,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126483257</v>
+        <v>127602418</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,37 +1218,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464760</v>
+        <v>464873</v>
       </c>
       <c r="R7" t="n">
-        <v>6784613</v>
+        <v>6784704</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,22 +1275,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:56</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:56</t>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,28 +1294,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126484941</v>
+        <v>127627129</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,34 +1324,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464775</v>
+        <v>464866</v>
       </c>
       <c r="R8" t="n">
-        <v>6784702</v>
+        <v>6784700</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,22 +1381,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:25</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:25</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,32 +1395,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126485359</v>
+        <v>126480241</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1464,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464793</v>
+        <v>464760</v>
       </c>
       <c r="R9" t="n">
-        <v>6784773</v>
+        <v>6784613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1484,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1494,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,14 +1521,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126485580</v>
+        <v>126480512</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1567,17 +1552,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464777</v>
+        <v>464743</v>
       </c>
       <c r="R10" t="n">
-        <v>6784791</v>
+        <v>6784623</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1591,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1601,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,57 +1616,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126480896</v>
+        <v>126480526</v>
       </c>
       <c r="B11" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464743</v>
+        <v>464766</v>
       </c>
       <c r="R11" t="n">
-        <v>6784623</v>
+        <v>6784628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,26 +1723,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126480624</v>
+        <v>126481466</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1781,14 +1766,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464766</v>
+        <v>464730</v>
       </c>
       <c r="R12" t="n">
-        <v>6784628</v>
+        <v>6784658</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,44 +1830,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126481544</v>
+        <v>126481494</v>
       </c>
       <c r="B13" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464778</v>
+        <v>464766</v>
       </c>
       <c r="R13" t="n">
-        <v>6784647</v>
+        <v>6784648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,50 +1949,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126481501</v>
+        <v>126481699</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464730</v>
+        <v>464778</v>
       </c>
       <c r="R14" t="n">
-        <v>6784658</v>
+        <v>6784647</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,26 +2044,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126485215</v>
+        <v>126482131</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2111,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464798</v>
+        <v>464774</v>
       </c>
       <c r="R15" t="n">
-        <v>6784753</v>
+        <v>6784611</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,14 +2163,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126485112</v>
+        <v>126482224</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2218,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464857</v>
+        <v>464765</v>
       </c>
       <c r="R16" t="n">
-        <v>6784710</v>
+        <v>6784612</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,14 +2270,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126481969</v>
+        <v>126482400</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2328,7 +2308,7 @@
         <v>464778</v>
       </c>
       <c r="R17" t="n">
-        <v>6784647</v>
+        <v>6784658</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,14 +2377,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126485040</v>
+        <v>126482486</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2428,14 +2408,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464849</v>
+        <v>464743</v>
       </c>
       <c r="R18" t="n">
-        <v>6784700</v>
+        <v>6784670</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,62 +2472,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126484808</v>
+        <v>126482505</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464775</v>
+        <v>464732</v>
       </c>
       <c r="R19" t="n">
-        <v>6784702</v>
+        <v>6784654</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,44 +2579,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126483693</v>
+        <v>126483268</v>
       </c>
       <c r="B20" t="n">
-        <v>98278</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464741</v>
+        <v>464732</v>
       </c>
       <c r="R20" t="n">
-        <v>6784664</v>
+        <v>6784658</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,14 +2698,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126481494</v>
+        <v>126484512</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2758,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464766</v>
+        <v>464760</v>
       </c>
       <c r="R21" t="n">
-        <v>6784648</v>
+        <v>6784680</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,14 +2805,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126484773</v>
+        <v>126484814</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2865,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464760</v>
+        <v>464806</v>
       </c>
       <c r="R22" t="n">
-        <v>6784680</v>
+        <v>6784704</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,14 +2912,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126482413</v>
+        <v>126484941</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2968,14 +2943,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464778</v>
+        <v>464775</v>
       </c>
       <c r="R23" t="n">
-        <v>6784658</v>
+        <v>6784702</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3017,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,62 +3007,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126485436</v>
+        <v>126484942</v>
       </c>
       <c r="B24" t="n">
-        <v>57479</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464793</v>
+        <v>464828</v>
       </c>
       <c r="R24" t="n">
-        <v>6784773</v>
+        <v>6784703</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3156,14 +3126,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126481466</v>
+        <v>126485023</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3191,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464730</v>
+        <v>464772</v>
       </c>
       <c r="R25" t="n">
-        <v>6784658</v>
+        <v>6784708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,45 +3233,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126480574</v>
+        <v>126485026</v>
       </c>
       <c r="B26" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464743</v>
+        <v>464849</v>
       </c>
       <c r="R26" t="n">
-        <v>6784623</v>
+        <v>6784700</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3343,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3358,57 +3328,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126485124</v>
+        <v>126485104</v>
       </c>
       <c r="B27" t="n">
-        <v>80119</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464772</v>
+        <v>464857</v>
       </c>
       <c r="R27" t="n">
-        <v>6784708</v>
+        <v>6784710</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3450,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3465,26 +3435,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126485741</v>
+        <v>126485142</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3512,13 +3482,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464743</v>
+        <v>464821</v>
       </c>
       <c r="R28" t="n">
-        <v>6784824</v>
+        <v>6784726</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3558,11 +3528,6 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie på ca 50 meter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,14 +3554,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126480512</v>
+        <v>126485215</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3620,14 +3585,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464743</v>
+        <v>464798</v>
       </c>
       <c r="R29" t="n">
-        <v>6784623</v>
+        <v>6784753</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3659,7 +3624,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3634,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3684,26 +3649,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126483188</v>
+        <v>126485359</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3731,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464732</v>
+        <v>464793</v>
       </c>
       <c r="R30" t="n">
-        <v>6784654</v>
+        <v>6784773</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3803,53 +3768,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126483169</v>
+        <v>126485580</v>
       </c>
       <c r="B31" t="n">
-        <v>57654</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464732</v>
+        <v>464777</v>
       </c>
       <c r="R31" t="n">
-        <v>6784654</v>
+        <v>6784791</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3915,14 +3875,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126483268</v>
+        <v>126485608</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3950,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464732</v>
+        <v>464769</v>
       </c>
       <c r="R32" t="n">
-        <v>6784658</v>
+        <v>6784801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4022,41 +3982,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126483802</v>
+        <v>126485702</v>
       </c>
       <c r="B33" t="n">
-        <v>97241</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>224363</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464766</v>
+        <v>464760</v>
       </c>
       <c r="R33" t="n">
-        <v>6784682</v>
+        <v>6784816</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4088,7 +4052,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4098,7 +4062,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,26 +4077,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126485629</v>
+        <v>126485741</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4160,13 +4124,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464769</v>
+        <v>464743</v>
       </c>
       <c r="R34" t="n">
-        <v>6784801</v>
+        <v>6784824</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4206,6 +4170,11 @@
       <c r="AB34" t="inlineStr">
         <is>
           <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie på ca 50 meter.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4232,32 +4201,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126492740</v>
+        <v>126585245</v>
       </c>
       <c r="B35" t="n">
-        <v>79012</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4270,13 +4239,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464775</v>
+        <v>464749</v>
       </c>
       <c r="R35" t="n">
-        <v>6784654</v>
+        <v>6784609</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4300,17 +4269,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Miljöbild. Rikligt med garnlav synligt bakom avverkningsanmälan, Bergkvist Siljan.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4326,63 +4305,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126492750</v>
+        <v>126585428</v>
       </c>
       <c r="B36" t="n">
-        <v>79012</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464757</v>
+        <v>464725</v>
       </c>
       <c r="R36" t="n">
-        <v>6784808</v>
+        <v>6784623</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4406,17 +4382,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4425,51 +4406,50 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126480564</v>
+        <v>126585536</v>
       </c>
       <c r="B37" t="n">
-        <v>79012</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4479,13 +4459,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464766</v>
+        <v>464689</v>
       </c>
       <c r="R37" t="n">
-        <v>6784628</v>
+        <v>6784645</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4509,22 +4489,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4551,32 +4531,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126483158</v>
+        <v>126585619</v>
       </c>
       <c r="B38" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4586,10 +4566,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464732</v>
+        <v>464704</v>
       </c>
       <c r="R38" t="n">
-        <v>6784654</v>
+        <v>6784647</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4616,22 +4596,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4658,32 +4638,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126485267</v>
+        <v>126585736</v>
       </c>
       <c r="B39" t="n">
-        <v>79012</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4693,10 +4673,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464793</v>
+        <v>464720</v>
       </c>
       <c r="R39" t="n">
-        <v>6784773</v>
+        <v>6784658</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4723,22 +4703,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4765,45 +4745,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126482418</v>
+        <v>126586047</v>
       </c>
       <c r="B40" t="n">
-        <v>79004</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464743</v>
+        <v>464730</v>
       </c>
       <c r="R40" t="n">
-        <v>6784670</v>
+        <v>6784662</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,22 +4810,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4860,57 +4840,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126481132</v>
+        <v>126586092</v>
       </c>
       <c r="B41" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464743</v>
+        <v>464712</v>
       </c>
       <c r="R41" t="n">
-        <v>6784623</v>
+        <v>6784680</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4937,22 +4917,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4967,26 +4947,26 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126482374</v>
+        <v>126586589</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5014,10 +4994,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464765</v>
+        <v>464639</v>
       </c>
       <c r="R42" t="n">
-        <v>6784612</v>
+        <v>6784741</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5044,22 +5024,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5086,50 +5066,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126481482</v>
+        <v>126586650</v>
       </c>
       <c r="B43" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464730</v>
+        <v>464649</v>
       </c>
       <c r="R43" t="n">
-        <v>6784658</v>
+        <v>6784725</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5156,22 +5131,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5186,26 +5161,26 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126485023</v>
+        <v>126586891</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5229,14 +5204,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464772</v>
+        <v>464671</v>
       </c>
       <c r="R44" t="n">
-        <v>6784708</v>
+        <v>6784711</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5263,22 +5238,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5293,57 +5268,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126482525</v>
+        <v>126587405</v>
       </c>
       <c r="B45" t="n">
-        <v>103803</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västersvedbäcken, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464743</v>
+        <v>464814</v>
       </c>
       <c r="R45" t="n">
-        <v>6784670</v>
+        <v>6784654</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5370,22 +5345,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5400,57 +5375,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126585639</v>
+        <v>126588667</v>
       </c>
       <c r="B46" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464704</v>
+        <v>464831</v>
       </c>
       <c r="R46" t="n">
-        <v>6784647</v>
+        <v>6784672</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5482,7 +5460,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5492,7 +5470,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Miljöbilder för närområdet</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5501,6 +5484,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5519,14 +5503,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126589776</v>
+        <v>126589398</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5554,10 +5538,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464839</v>
+        <v>464858</v>
       </c>
       <c r="R47" t="n">
-        <v>6784720</v>
+        <v>6784712</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5626,14 +5610,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126586891</v>
+        <v>126589408</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5661,10 +5645,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464671</v>
+        <v>464857</v>
       </c>
       <c r="R48" t="n">
-        <v>6784711</v>
+        <v>6784712</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5696,7 +5680,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5706,7 +5690,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5733,14 +5717,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126590186</v>
+        <v>126589776</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5768,10 +5752,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464816</v>
+        <v>464839</v>
       </c>
       <c r="R49" t="n">
-        <v>6784753</v>
+        <v>6784720</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5840,14 +5824,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126585619</v>
+        <v>126589816</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5875,10 +5859,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464704</v>
+        <v>464831</v>
       </c>
       <c r="R50" t="n">
-        <v>6784647</v>
+        <v>6784718</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5910,7 +5894,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5920,7 +5904,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5947,14 +5931,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126590867</v>
+        <v>126590106</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5982,10 +5966,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464730</v>
+        <v>464803</v>
       </c>
       <c r="R51" t="n">
-        <v>6784826</v>
+        <v>6784725</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6017,7 +6001,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6027,7 +6011,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6054,14 +6038,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126585460</v>
+        <v>126590186</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -6089,13 +6073,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464725</v>
+        <v>464816</v>
       </c>
       <c r="R52" t="n">
-        <v>6784623</v>
+        <v>6784753</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6124,7 +6108,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6134,7 +6118,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6161,14 +6145,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126591332</v>
+        <v>126590480</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6196,10 +6180,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464744</v>
+        <v>464755</v>
       </c>
       <c r="R53" t="n">
-        <v>6784847</v>
+        <v>6784795</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6268,14 +6252,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126589735</v>
+        <v>126590826</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6303,10 +6287,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464857</v>
+        <v>464741</v>
       </c>
       <c r="R54" t="n">
-        <v>6784712</v>
+        <v>6784807</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6338,7 +6322,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6348,7 +6332,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6375,14 +6359,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126591518</v>
+        <v>126590840</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6410,10 +6394,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464757</v>
+        <v>464734</v>
       </c>
       <c r="R55" t="n">
-        <v>6784856</v>
+        <v>6784815</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6482,14 +6466,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126585536</v>
+        <v>126590850</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6517,13 +6501,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464689</v>
+        <v>464724</v>
       </c>
       <c r="R56" t="n">
-        <v>6784645</v>
+        <v>6784810</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6552,7 +6536,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6562,7 +6546,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6589,14 +6573,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126585736</v>
+        <v>126590867</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6624,10 +6608,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464720</v>
+        <v>464730</v>
       </c>
       <c r="R57" t="n">
-        <v>6784658</v>
+        <v>6784826</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6659,7 +6643,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6669,7 +6653,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6696,14 +6680,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126589398</v>
+        <v>126591007</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -6731,10 +6715,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464858</v>
+        <v>464744</v>
       </c>
       <c r="R58" t="n">
-        <v>6784712</v>
+        <v>6784847</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6766,7 +6750,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6776,7 +6760,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6803,14 +6787,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126585258</v>
+        <v>126591506</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6838,10 +6822,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464749</v>
+        <v>464757</v>
       </c>
       <c r="R59" t="n">
-        <v>6784609</v>
+        <v>6784856</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6873,7 +6857,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6883,7 +6867,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6910,32 +6894,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126589767</v>
+        <v>126591615</v>
       </c>
       <c r="B60" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6945,10 +6929,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464839</v>
+        <v>464711</v>
       </c>
       <c r="R60" t="n">
-        <v>6784720</v>
+        <v>6784812</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6980,7 +6964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6990,7 +6974,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7017,14 +7001,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126586650</v>
+        <v>126592098</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -7052,10 +7036,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464649</v>
+        <v>464676</v>
       </c>
       <c r="R61" t="n">
-        <v>6784725</v>
+        <v>6784780</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7087,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7097,7 +7081,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Garn vid rullstensås</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7124,50 +7113,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126585359</v>
+        <v>127528615</v>
       </c>
       <c r="B62" t="n">
-        <v>57654</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464766</v>
+        <v>464875</v>
       </c>
       <c r="R62" t="n">
-        <v>6784628</v>
+        <v>6784695</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7194,22 +7178,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7236,14 +7220,14 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126586047</v>
+        <v>127530663</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -7271,10 +7255,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>464730</v>
+        <v>464850</v>
       </c>
       <c r="R63" t="n">
-        <v>6784662</v>
+        <v>6784699</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7301,22 +7285,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7343,14 +7327,14 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126586092</v>
+        <v>127536063</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -7378,10 +7362,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464712</v>
+        <v>464819</v>
       </c>
       <c r="R64" t="n">
-        <v>6784680</v>
+        <v>6784639</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7408,22 +7392,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7450,45 +7434,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126586980</v>
+        <v>127627114</v>
       </c>
       <c r="B65" t="n">
-        <v>79632</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464671</v>
+        <v>464868</v>
       </c>
       <c r="R65" t="n">
-        <v>6784711</v>
+        <v>6784685</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7515,22 +7502,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7539,68 +7521,67 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126585897</v>
+        <v>127627165</v>
       </c>
       <c r="B66" t="n">
-        <v>57654</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464732</v>
+        <v>464808</v>
       </c>
       <c r="R66" t="n">
-        <v>6784658</v>
+        <v>6784637</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7627,22 +7608,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7651,50 +7622,51 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126586084</v>
+        <v>127627174</v>
       </c>
       <c r="B67" t="n">
-        <v>75138</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7707,10 +7679,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464712</v>
+        <v>464796</v>
       </c>
       <c r="R67" t="n">
-        <v>6784680</v>
+        <v>6784631</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7737,27 +7709,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Miljöbilder för närområdet</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7773,54 +7730,49 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127020539</v>
+        <v>127627233</v>
       </c>
       <c r="B68" t="n">
-        <v>97339</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7828,13 +7780,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464774</v>
+        <v>464804</v>
       </c>
       <c r="R68" t="n">
-        <v>6784776</v>
+        <v>6784620</v>
       </c>
       <c r="S68" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7858,17 +7810,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt till sparsamt i området</t>
+          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7884,22 +7836,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127020521</v>
+        <v>126482418</v>
       </c>
       <c r="B69" t="n">
-        <v>97333</v>
+        <v>79351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7907,41 +7859,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464774</v>
+        <v>464743</v>
       </c>
       <c r="R69" t="n">
-        <v>6784776</v>
+        <v>6784670</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7968,40 +7916,49 @@
           <t>2025-07-07</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127531842</v>
+        <v>126487403</v>
       </c>
       <c r="B70" t="n">
-        <v>79029</v>
+        <v>83307</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8009,21 +7966,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8033,10 +7990,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464850</v>
+        <v>464751</v>
       </c>
       <c r="R70" t="n">
-        <v>6784699</v>
+        <v>6784883</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8063,22 +8020,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8102,6 +8059,3803 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126586084</v>
+      </c>
+      <c r="B71" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>464712</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6784680</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Miljöbilder för närområdet</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127518186</v>
+      </c>
+      <c r="B72" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>464838</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6784648</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127521304</v>
+      </c>
+      <c r="B73" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>464831</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6784672</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Bild på kraftig gran vid gränsen</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127524724</v>
+      </c>
+      <c r="B74" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>464825</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6784652</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127627101</v>
+      </c>
+      <c r="B75" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>464854</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6784664</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126480574</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>464743</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6784623</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126480896</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>464743</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6784623</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126481544</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>464778</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6784647</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126586980</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>464671</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6784711</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126485124</v>
+      </c>
+      <c r="B80" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>464772</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6784708</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126481501</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>464730</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6784658</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126483169</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>464732</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6784654</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126485146</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>464765</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6784693</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126585359</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>464766</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6784628</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126585897</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>464732</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6784658</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126485436</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57774</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>464793</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6784773</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126485010</v>
+      </c>
+      <c r="B87" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>464828</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6784703</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126481482</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>464730</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6784658</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126483158</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>464732</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6784654</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126484808</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>464775</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6784702</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126485952</v>
+      </c>
+      <c r="B91" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>464750</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6784735</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126585639</v>
+      </c>
+      <c r="B92" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>464704</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6784647</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126589767</v>
+      </c>
+      <c r="B93" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>464839</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6784720</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>126589818</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>464831</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6784718</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>126483693</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>464741</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6784664</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>127020539</v>
+      </c>
+      <c r="B96" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>464774</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6784776</v>
+      </c>
+      <c r="S96" t="n">
+        <v>50</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt till sparsamt i området</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>127020521</v>
+      </c>
+      <c r="B97" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>464774</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6784776</v>
+      </c>
+      <c r="S97" t="n">
+        <v>50</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>126482525</v>
+      </c>
+      <c r="B98" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Västersvedbäcken, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>464743</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6784670</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127627149</v>
+      </c>
+      <c r="B99" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>464860</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6784675</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126483802</v>
+      </c>
+      <c r="B100" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>464766</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6784682</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>126481132</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>464743</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6784623</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>126481487</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>464766</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6784648</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>127530350</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>464867</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6784698</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Bilder på gran med garn</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>126485068</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>464772</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6784708</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>126492727</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>464813</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6784739</v>
+      </c>
+      <c r="S105" t="n">
+        <v>25</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY105"/>
+  <dimension ref="A1:AZ105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126480564</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485267</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126492740</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126492750</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126492793</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127602418</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127627129</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126480241</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126480512</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126480526</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,6 +1894,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126481466</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126481494</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126481699</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2160,6 +2230,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126482131</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126482224</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2374,6 +2454,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126482400</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2481,6 +2566,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126482486</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2588,6 +2678,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126482505</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2695,6 +2790,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126483268</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2802,6 +2902,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126484512</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2909,6 +3014,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126484814</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3016,6 +3126,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126484941</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3123,6 +3238,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126484942</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3230,6 +3350,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485023</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3337,6 +3462,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3444,6 +3574,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485104</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3551,6 +3686,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485142</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3658,6 +3798,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485215</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3765,6 +3910,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485359</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3872,6 +4022,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485580</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3979,6 +4134,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485608</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4086,6 +4246,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485702</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4198,6 +4363,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485741</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4314,6 +4484,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126585245</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4421,6 +4596,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126585428</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4528,6 +4708,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126585536</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4635,6 +4820,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126585619</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4742,6 +4932,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126585736</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4849,6 +5044,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126586047</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4956,6 +5156,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126586092</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5063,6 +5268,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126586589</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5170,6 +5380,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126586650</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5277,6 +5492,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126586891</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5384,6 +5604,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126587405</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5500,6 +5725,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126588667</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5607,6 +5837,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126589398</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5714,6 +5949,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126589408</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5821,6 +6061,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126589776</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5928,6 +6173,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126589816</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6035,6 +6285,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590106</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6142,6 +6397,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590186</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6249,6 +6509,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590480</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6356,6 +6621,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590826</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6463,6 +6733,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590840</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6570,6 +6845,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590850</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6677,6 +6957,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590867</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6784,6 +7069,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591007</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6891,6 +7181,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591506</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6998,6 +7293,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591615</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7110,6 +7410,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126592098</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7217,6 +7522,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127528615</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7324,6 +7634,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127530663</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7431,6 +7746,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127536063</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7537,6 +7857,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127627114</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7638,6 +7963,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127627165</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7739,6 +8069,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127627174</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7845,6 +8180,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127627233</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7952,6 +8292,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126482418</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8059,6 +8404,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487403</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8175,6 +8525,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126586084</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8282,6 +8637,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127518186</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8394,6 +8754,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127521304</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8501,6 +8866,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127524724</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8602,6 +8972,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127627101</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8709,6 +9084,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126480574</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8816,6 +9196,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126480896</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8923,6 +9308,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126481544</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9030,6 +9420,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126586980</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9137,6 +9532,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485124</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9249,6 +9649,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126481501</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9361,6 +9766,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126483169</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9473,6 +9883,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485146</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9585,6 +10000,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126585359</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9697,6 +10117,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126585897</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9809,6 +10234,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485436</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9921,6 +10351,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485010</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10033,6 +10468,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126481482</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10140,6 +10580,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126483158</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10252,6 +10697,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126484808</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10364,6 +10814,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485952</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10471,6 +10926,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126585639</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10578,6 +11038,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126589767</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10685,6 +11150,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126589818</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10792,6 +11262,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126483693</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10903,6 +11378,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127020539</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11005,6 +11485,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127020521</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11112,6 +11597,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126482525</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11214,6 +11704,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127627149</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11317,6 +11812,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126483802</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11424,6 +11924,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126481132</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11531,6 +12036,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126481487</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11643,6 +12153,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127530350</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11750,6 +12265,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485068</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11856,8 +12376,119 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126492727</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>